--- a/Intersecciones/excels/LIMA-LIMA-VILLA_MARIA_DEL_TRIUNFO.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-VILLA_MARIA_DEL_TRIUNFO.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida 7 de Junio / Avenida 2 de Mayo</t>
+          <t>Avenida 2 de Mayo / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">

--- a/Intersecciones/excels/LIMA-LIMA-VILLA_MARIA_DEL_TRIUNFO.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-VILLA_MARIA_DEL_TRIUNFO.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>150143</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-100911</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>150143</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-12.1430927</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>150143</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>150143</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-153813</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>150143</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-12.167602</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>150143</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>150143</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-153866</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>150143</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-12.1598887</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>150143</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>150143</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-137842</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>150143</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-12.1832043</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>150143</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>150143</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-153997</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>150143</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-12.173071</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>150143</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>150143</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-652612</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>150143</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-12.1453517</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>150143</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>150143</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-338515</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>150143</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-12.1504865</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>150143</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>150143</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-338513</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>150143</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-12.1421071</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>150143</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>150143</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-338512</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>150143</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-12.1429577</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>150143</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>150143</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-338511</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>150143</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>VILLA MARIA DEL TRIUNFO</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-12.1459771</t>
@@ -992,11 +942,6 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>150143</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/LIMA-LIMA-VILLA_MARIA_DEL_TRIUNFO.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-VILLA_MARIA_DEL_TRIUNFO.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/LIMA-LIMA-VILLA_MARIA_DEL_TRIUNFO.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-VILLA_MARIA_DEL_TRIUNFO.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+          <t>VILLA MARIA DEL TRIUNFO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+          <t>VILLA MARIA DEL TRIUNFO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+          <t>VILLA MARIA DEL TRIUNFO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+          <t>VILLA MARIA DEL TRIUNFO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+          <t>VILLA MARIA DEL TRIUNFO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+          <t>VILLA MARIA DEL TRIUNFO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+          <t>VILLA MARIA DEL TRIUNFO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+          <t>VILLA MARIA DEL TRIUNFO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+          <t>VILLA MARIA DEL TRIUNFO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VILLA_MARIA_DEL_TRIUNFO</t>
+          <t>VILLA MARIA DEL TRIUNFO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">

--- a/Intersecciones/excels/LIMA-LIMA-VILLA_MARIA_DEL_TRIUNFO.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-VILLA_MARIA_DEL_TRIUNFO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/LIMA-LIMA-VILLA_MARIA_DEL_TRIUNFO.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-VILLA_MARIA_DEL_TRIUNFO.xlsx
@@ -585,17 +585,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-12.1598887</t>
+          <t>-12.16156</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-76.9393384</t>
+          <t>-76.949194</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida El Triunfo / Calle Ricardo Palma</t>
+          <t>Jiron Progreso / Calle San Martin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-12.1832043</t>
+          <t>-12.15815</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-76.9249334</t>
+          <t>-76.9405</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Los Incas / Jirón Tres Marías</t>
+          <t>Av. San Jose / Calle Ricardo Palma</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-12.1453517</t>
+          <t>-12.172865</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-76.9531682</t>
+          <t>-76.943018</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida Jose de San Martin / Avenida Prolongación Luis Pardo</t>
+          <t>Jiron Progreso / Jiron Carlos Dellepiani</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">

--- a/Intersecciones/excels/LIMA-LIMA-VILLA_MARIA_DEL_TRIUNFO.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-VILLA_MARIA_DEL_TRIUNFO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,22 +486,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-100911</t>
+          <t>I-652612</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-12.1430927</t>
+          <t>-12.172865</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-76.9539633</t>
+          <t>-76.943018</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Guardia Civil / Avenida Simón Bolívar</t>
+          <t>Jiron Progreso / Jiron Carlos Dellepiani</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,22 +533,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-153813</t>
+          <t>I-338515</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-12.167602</t>
+          <t>-12.1504865</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-76.945024</t>
+          <t>-76.9070259</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Pedro Tejada / Jirón Progreso</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -580,27 +580,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-153866</t>
+          <t>I-338513</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-12.16156</t>
+          <t>-12.1421071</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-76.949194</t>
+          <t>-76.9052535</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Jiron Progreso / Calle San Martin</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -627,27 +627,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-137842</t>
+          <t>I-338512</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-12.15815</t>
+          <t>-12.1429577</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-76.9405</t>
+          <t>-76.9052778</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Av. San Jose / Calle Ricardo Palma</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-153997</t>
+          <t>I-338511</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-12.173071</t>
+          <t>-12.1459771</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-76.934408</t>
+          <t>-76.9055024</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida 2 de Mayo / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,27 +721,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-652612</t>
+          <t>I-153997</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-12.172865</t>
+          <t>-12.173071</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-76.943018</t>
+          <t>-76.934408</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Jiron Progreso / Jiron Carlos Dellepiani</t>
+          <t>Avenida 7 de Junio / Avenida 2 de Mayo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -768,27 +768,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-338515</t>
+          <t>I-153866</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-12.1504865</t>
+          <t>-12.16156</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-76.9070259</t>
+          <t>-76.949194</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jiron Progreso / Calle San Martin</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -815,22 +815,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-338513</t>
+          <t>I-153813</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-12.1421071</t>
+          <t>-12.167602</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-76.9052535</t>
+          <t>-76.945024</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Pedro Tejada / Jirón Progreso</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -862,22 +862,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-338512</t>
+          <t>I-15201</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-12.1429577</t>
+          <t>-12.1763323</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-76.9052778</t>
+          <t>-76.940786</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Nicolás de Piérola / Pasaje Peruanidad</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -909,27 +909,74 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-338511</t>
+          <t>I-137842</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-12.1459771</t>
+          <t>-12.15815</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-76.9055024</t>
+          <t>-76.9405</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Av. San Jose / Calle Ricardo Palma</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>150143</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VILLA MARIA DEL TRIUNFO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>I-100911</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-12.1430927</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-76.9539633</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Avenida Guardia Civil / Avenida Simón Bolívar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
